--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171D180F-611A-4723-8786-FD02F2120A90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B7DECC-64DA-49A4-BDF9-DA682C887F69}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1084,23 +1084,34 @@
       <c r="D16" s="1">
         <v>45</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1">
+        <f>37.4</f>
+        <v>37.4</v>
+      </c>
       <c r="F16" s="1">
         <v>35.1</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1">
+        <v>48.4</v>
+      </c>
       <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="J16" s="1">
         <v>12</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L16" s="1">
         <v>13.5</v>
       </c>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1116,23 +1127,34 @@
       <c r="D17" s="1">
         <v>45</v>
       </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="1">
+        <f>31.7</f>
+        <v>31.7</v>
+      </c>
       <c r="F17" s="1">
         <v>35.1</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1">
+        <v>48.5</v>
+      </c>
       <c r="H17" s="1">
         <v>30</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="J17" s="1">
         <v>12</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L17" s="1">
         <v>13.5</v>
       </c>
-      <c r="M17" s="1"/>
+      <c r="M17" s="1">
+        <v>4.9000000000000004</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1148,23 +1170,34 @@
       <c r="D18" s="1">
         <v>45</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <f>31.7+35</f>
+        <v>66.7</v>
+      </c>
       <c r="F18" s="1">
         <v>35.1</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1">
+        <v>48.5</v>
+      </c>
       <c r="H18" s="1">
         <v>30</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="J18" s="1">
         <v>12</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L18" s="1">
         <v>13.5</v>
       </c>
-      <c r="M18" s="1"/>
+      <c r="M18" s="1">
+        <v>4.9000000000000004</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -2286,23 +2319,34 @@
       <c r="D52" s="1">
         <v>15</v>
       </c>
-      <c r="E52" s="1"/>
+      <c r="E52" s="1">
+        <f>25.1</f>
+        <v>25.1</v>
+      </c>
       <c r="F52" s="1">
         <v>10</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1">
+        <v>24</v>
+      </c>
       <c r="H52" s="1">
         <v>7.4</v>
       </c>
-      <c r="I52" s="1"/>
+      <c r="I52" s="1">
+        <v>12.2</v>
+      </c>
       <c r="J52" s="1">
         <v>5</v>
       </c>
-      <c r="K52" s="1"/>
+      <c r="K52" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L52" s="1">
         <v>2.8</v>
       </c>
-      <c r="M52" s="1"/>
+      <c r="M52" s="1">
+        <v>7.6</v>
+      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
@@ -2318,23 +2362,34 @@
       <c r="D53" s="1">
         <v>15</v>
       </c>
-      <c r="E53" s="1"/>
+      <c r="E53" s="1">
+        <f>25.4</f>
+        <v>25.4</v>
+      </c>
       <c r="F53" s="1">
         <v>10</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1">
+        <v>24</v>
+      </c>
       <c r="H53" s="1">
         <v>7.4</v>
       </c>
-      <c r="I53" s="1"/>
+      <c r="I53" s="1">
+        <v>12.3</v>
+      </c>
       <c r="J53" s="1">
         <v>5</v>
       </c>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L53" s="1">
         <v>2.8</v>
       </c>
-      <c r="M53" s="1"/>
+      <c r="M53" s="1">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
@@ -2350,23 +2405,34 @@
       <c r="D54" s="1">
         <v>15</v>
       </c>
-      <c r="E54" s="1"/>
+      <c r="E54" s="1">
+        <f>25.4</f>
+        <v>25.4</v>
+      </c>
       <c r="F54" s="1">
         <v>10</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1">
+        <v>24.1</v>
+      </c>
       <c r="H54" s="1">
         <v>7.4</v>
       </c>
-      <c r="I54" s="1"/>
+      <c r="I54" s="1">
+        <v>12.3</v>
+      </c>
       <c r="J54" s="1">
         <v>5</v>
       </c>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1">
+        <v>6.7</v>
+      </c>
       <c r="L54" s="1">
         <v>2.8</v>
       </c>
-      <c r="M54" s="1"/>
+      <c r="M54" s="1">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
@@ -3488,23 +3554,34 @@
       <c r="D87" s="1">
         <v>22</v>
       </c>
-      <c r="E87" s="1"/>
+      <c r="E87" s="1">
+        <f>26.1</f>
+        <v>26.1</v>
+      </c>
       <c r="F87" s="1">
         <v>6</v>
       </c>
-      <c r="G87" s="1"/>
+      <c r="G87" s="1">
+        <v>11.4</v>
+      </c>
       <c r="H87" s="1">
         <v>4.5</v>
       </c>
-      <c r="I87" s="1"/>
+      <c r="I87" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J87" s="1">
         <v>5</v>
       </c>
-      <c r="K87" s="1"/>
+      <c r="K87" s="1">
+        <v>16.7</v>
+      </c>
       <c r="L87" s="1">
         <v>2.7</v>
       </c>
-      <c r="M87" s="1"/>
+      <c r="M87" s="1">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
@@ -3520,23 +3597,34 @@
       <c r="D88" s="1">
         <v>22</v>
       </c>
-      <c r="E88" s="1"/>
+      <c r="E88" s="1">
+        <f>26.5</f>
+        <v>26.5</v>
+      </c>
       <c r="F88" s="1">
         <v>6</v>
       </c>
-      <c r="G88" s="1"/>
+      <c r="G88" s="1">
+        <v>11.4</v>
+      </c>
       <c r="H88" s="1">
         <v>4.5</v>
       </c>
-      <c r="I88" s="1"/>
+      <c r="I88" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J88" s="1">
         <v>5</v>
       </c>
-      <c r="K88" s="1"/>
+      <c r="K88" s="1">
+        <v>16.7</v>
+      </c>
       <c r="L88" s="1">
         <v>2.7</v>
       </c>
-      <c r="M88" s="1"/>
+      <c r="M88" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
@@ -3552,23 +3640,34 @@
       <c r="D89" s="1">
         <v>22</v>
       </c>
-      <c r="E89" s="1"/>
+      <c r="E89" s="1">
+        <f>32.9</f>
+        <v>32.9</v>
+      </c>
       <c r="F89" s="1">
         <v>6</v>
       </c>
-      <c r="G89" s="1"/>
+      <c r="G89" s="1">
+        <v>11.4</v>
+      </c>
       <c r="H89" s="1">
         <v>4.5</v>
       </c>
-      <c r="I89" s="1"/>
+      <c r="I89" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J89" s="1">
         <v>5</v>
       </c>
-      <c r="K89" s="1"/>
+      <c r="K89" s="1">
+        <v>16.7</v>
+      </c>
       <c r="L89" s="1">
         <v>2.7</v>
       </c>
-      <c r="M89" s="1"/>
+      <c r="M89" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B7DECC-64DA-49A4-BDF9-DA682C887F69}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8474C0-D5F8-4C68-B09C-D49FFC0EB5C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1213,23 +1213,34 @@
       <c r="D19" s="1">
         <v>45</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1">
+        <f>35.6+35</f>
+        <v>70.599999999999994</v>
+      </c>
       <c r="F19" s="1">
         <v>35.1</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1">
+        <v>35.799999999999997</v>
+      </c>
       <c r="H19" s="1">
         <v>30</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>41.8</v>
+      </c>
       <c r="J19" s="1">
         <v>12</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1">
+        <v>10.6</v>
+      </c>
       <c r="L19" s="1">
         <v>13.5</v>
       </c>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1712,21 +1723,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1770,13 +1781,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1801,9 +1812,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2448,23 +2459,34 @@
       <c r="D55" s="1">
         <v>15</v>
       </c>
-      <c r="E55" s="1"/>
+      <c r="E55" s="1">
+        <f>17.2+15.3</f>
+        <v>32.5</v>
+      </c>
       <c r="F55" s="1">
         <v>10</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1">
+        <v>22.2</v>
+      </c>
       <c r="H55" s="1">
         <v>7.4</v>
       </c>
-      <c r="I55" s="1"/>
+      <c r="I55" s="1">
+        <v>10</v>
+      </c>
       <c r="J55" s="1">
         <v>5</v>
       </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1">
+        <v>5.7</v>
+      </c>
       <c r="L55" s="1">
         <v>2.8</v>
       </c>
-      <c r="M55" s="1"/>
+      <c r="M55" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -2947,21 +2969,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3005,13 +3027,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3036,9 +3058,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3683,23 +3705,34 @@
       <c r="D90" s="1">
         <v>22</v>
       </c>
-      <c r="E90" s="1"/>
+      <c r="E90" s="1">
+        <f>38.5</f>
+        <v>38.5</v>
+      </c>
       <c r="F90" s="1">
         <v>6</v>
       </c>
-      <c r="G90" s="1"/>
+      <c r="G90" s="1">
+        <v>14.9</v>
+      </c>
       <c r="H90" s="1">
         <v>4.5</v>
       </c>
-      <c r="I90" s="1"/>
+      <c r="I90" s="1">
+        <v>5.2</v>
+      </c>
       <c r="J90" s="1">
         <v>5</v>
       </c>
-      <c r="K90" s="1"/>
+      <c r="K90" s="1">
+        <v>15</v>
+      </c>
       <c r="L90" s="1">
         <v>2.7</v>
       </c>
-      <c r="M90" s="1"/>
+      <c r="M90" s="1">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
@@ -4183,6 +4216,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4192,24 +4243,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8474C0-D5F8-4C68-B09C-D49FFC0EB5C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341EDED9-EF25-4175-87E2-8D3647C12565}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1256,23 +1256,33 @@
       <c r="D20" s="1">
         <v>45</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1">
+        <v>60.8</v>
+      </c>
       <c r="F20" s="1">
         <v>35.1</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <v>42.7</v>
+      </c>
       <c r="H20" s="1">
         <v>30</v>
       </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1">
+        <v>33.5</v>
+      </c>
       <c r="J20" s="1">
         <v>12</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1">
+        <v>7.7</v>
+      </c>
       <c r="L20" s="1">
         <v>13.5</v>
       </c>
-      <c r="M20" s="1"/>
+      <c r="M20" s="1">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1723,21 +1733,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1781,13 +1791,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1812,9 +1822,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2502,23 +2512,33 @@
       <c r="D56" s="1">
         <v>15</v>
       </c>
-      <c r="E56" s="1"/>
+      <c r="E56" s="1">
+        <v>39.1</v>
+      </c>
       <c r="F56" s="1">
         <v>10</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1">
+        <v>19.5</v>
+      </c>
       <c r="H56" s="1">
         <v>7.4</v>
       </c>
-      <c r="I56" s="1"/>
+      <c r="I56" s="1">
+        <v>8.1</v>
+      </c>
       <c r="J56" s="1">
         <v>5</v>
       </c>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="L56" s="1">
         <v>2.8</v>
       </c>
-      <c r="M56" s="1"/>
+      <c r="M56" s="1">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
@@ -2969,21 +2989,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3027,13 +3047,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3058,9 +3078,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3748,23 +3768,33 @@
       <c r="D91" s="1">
         <v>22</v>
       </c>
-      <c r="E91" s="1"/>
+      <c r="E91" s="1">
+        <v>31.3</v>
+      </c>
       <c r="F91" s="1">
         <v>6</v>
       </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1">
+        <v>13.1</v>
+      </c>
       <c r="H91" s="1">
         <v>4.5</v>
       </c>
-      <c r="I91" s="1"/>
+      <c r="I91" s="1">
+        <v>4</v>
+      </c>
       <c r="J91" s="1">
         <v>5</v>
       </c>
-      <c r="K91" s="1"/>
+      <c r="K91" s="1">
+        <v>20.7</v>
+      </c>
       <c r="L91" s="1">
         <v>2.7</v>
       </c>
-      <c r="M91" s="1"/>
+      <c r="M91" s="1">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
@@ -4216,6 +4246,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -4225,24 +4273,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341EDED9-EF25-4175-87E2-8D3647C12565}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA33582E-5E13-42F6-A8CF-680FC13B8853}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1298,23 +1298,34 @@
       <c r="D21" s="1">
         <v>45</v>
       </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1">
+        <f>36.6</f>
+        <v>36.6</v>
+      </c>
       <c r="F21" s="1">
         <v>35.1</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1">
+        <v>32.5</v>
+      </c>
       <c r="H21" s="1">
         <v>30</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1">
+        <v>26.9</v>
+      </c>
       <c r="J21" s="1">
         <v>12</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1">
+        <v>5.4</v>
+      </c>
       <c r="L21" s="1">
         <v>13.5</v>
       </c>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1733,21 +1744,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1791,13 +1802,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1822,9 +1833,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2554,23 +2565,34 @@
       <c r="D57" s="1">
         <v>15</v>
       </c>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1">
+        <f>32.7</f>
+        <v>32.700000000000003</v>
+      </c>
       <c r="F57" s="1">
         <v>10</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1">
+        <v>17.399999999999999</v>
+      </c>
       <c r="H57" s="1">
         <v>7.4</v>
       </c>
-      <c r="I57" s="1"/>
+      <c r="I57" s="1">
+        <v>6.7</v>
+      </c>
       <c r="J57" s="1">
         <v>5</v>
       </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1">
+        <v>3.1</v>
+      </c>
       <c r="L57" s="1">
         <v>2.8</v>
       </c>
-      <c r="M57" s="1"/>
+      <c r="M57" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -2989,21 +3011,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3047,13 +3069,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3078,9 +3100,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3810,23 +3832,34 @@
       <c r="D92" s="1">
         <v>22</v>
       </c>
-      <c r="E92" s="1"/>
+      <c r="E92" s="1">
+        <f>24.7</f>
+        <v>24.7</v>
+      </c>
       <c r="F92" s="1">
         <v>6</v>
       </c>
-      <c r="G92" s="1"/>
+      <c r="G92" s="1">
+        <v>14.6</v>
+      </c>
       <c r="H92" s="1">
         <v>4.5</v>
       </c>
-      <c r="I92" s="1"/>
+      <c r="I92" s="1">
+        <v>13.4</v>
+      </c>
       <c r="J92" s="1">
         <v>5</v>
       </c>
-      <c r="K92" s="1"/>
+      <c r="K92" s="1">
+        <v>18.5</v>
+      </c>
       <c r="L92" s="1">
         <v>2.7</v>
       </c>
-      <c r="M92" s="1"/>
+      <c r="M92" s="1">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
@@ -4246,6 +4279,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4255,24 +4306,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA33582E-5E13-42F6-A8CF-680FC13B8853}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01799E7F-53B7-474E-8DAF-24098F51A843}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1341,23 +1341,34 @@
       <c r="D22" s="1">
         <v>45</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1">
+        <f>16.8+35+14</f>
+        <v>65.8</v>
+      </c>
       <c r="F22" s="1">
         <v>35.1</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1">
+        <v>56</v>
+      </c>
       <c r="H22" s="1">
         <v>30</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1">
+        <v>44.8</v>
+      </c>
       <c r="J22" s="1">
         <v>12</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1">
+        <v>4.8</v>
+      </c>
       <c r="L22" s="1">
         <v>13.5</v>
       </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1">
+        <v>17.5</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1744,21 +1755,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1802,13 +1813,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1833,9 +1844,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2608,23 +2619,34 @@
       <c r="D58" s="1">
         <v>15</v>
       </c>
-      <c r="E58" s="1"/>
+      <c r="E58" s="1">
+        <f>26.2+15</f>
+        <v>41.2</v>
+      </c>
       <c r="F58" s="1">
         <v>10</v>
       </c>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1">
+        <v>15.8</v>
+      </c>
       <c r="H58" s="1">
         <v>7.4</v>
       </c>
-      <c r="I58" s="1"/>
+      <c r="I58" s="1">
+        <v>18.7</v>
+      </c>
       <c r="J58" s="1">
         <v>5</v>
       </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1">
+        <v>2.4</v>
+      </c>
       <c r="L58" s="1">
         <v>2.8</v>
       </c>
-      <c r="M58" s="1"/>
+      <c r="M58" s="1">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
@@ -3011,21 +3033,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3069,13 +3091,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3100,9 +3122,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3875,23 +3897,34 @@
       <c r="D93" s="1">
         <v>22</v>
       </c>
-      <c r="E93" s="1"/>
+      <c r="E93" s="1">
+        <f>31.8</f>
+        <v>31.8</v>
+      </c>
       <c r="F93" s="1">
         <v>6</v>
       </c>
-      <c r="G93" s="1"/>
+      <c r="G93" s="1">
+        <v>12.6</v>
+      </c>
       <c r="H93" s="1">
         <v>4.5</v>
       </c>
-      <c r="I93" s="1"/>
+      <c r="I93" s="1">
+        <v>11.3</v>
+      </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
-      <c r="K93" s="1"/>
+      <c r="K93" s="1">
+        <v>7.3</v>
+      </c>
       <c r="L93" s="1">
         <v>2.7</v>
       </c>
-      <c r="M93" s="1"/>
+      <c r="M93" s="1">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
@@ -4279,6 +4312,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -4288,24 +4339,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01799E7F-53B7-474E-8DAF-24098F51A843}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E3FCE5-B99F-4572-B2DA-279AF09BB54C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1384,23 +1384,33 @@
       <c r="D23" s="1">
         <v>45</v>
       </c>
-      <c r="E23" s="1"/>
+      <c r="E23" s="1">
+        <v>39.6</v>
+      </c>
       <c r="F23" s="1">
         <v>35.1</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1">
+        <v>46</v>
+      </c>
       <c r="H23" s="1">
         <v>30</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>37.700000000000003</v>
+      </c>
       <c r="J23" s="1">
         <v>12</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1">
+        <v>3.1</v>
+      </c>
       <c r="L23" s="1">
         <v>13.5</v>
       </c>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1416,23 +1426,33 @@
       <c r="D24" s="1">
         <v>45</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1">
+        <v>39.6</v>
+      </c>
       <c r="F24" s="1">
         <v>35.1</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1">
+        <v>56.3</v>
+      </c>
       <c r="H24" s="1">
         <v>30</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1">
+        <v>37.700000000000003</v>
+      </c>
       <c r="J24" s="1">
         <v>12</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1">
+        <v>18.2</v>
+      </c>
       <c r="L24" s="1">
         <v>13.5</v>
       </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1448,23 +1468,33 @@
       <c r="D25" s="1">
         <v>45</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1">
+        <v>90.7</v>
+      </c>
       <c r="F25" s="1">
         <v>35.1</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1">
+        <v>56.3</v>
+      </c>
       <c r="H25" s="1">
         <v>30</v>
       </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1">
+        <v>37.700000000000003</v>
+      </c>
       <c r="J25" s="1">
         <v>12</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1">
+        <v>13.5</v>
+      </c>
       <c r="L25" s="1">
         <v>13.5</v>
       </c>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -2662,23 +2692,33 @@
       <c r="D59" s="1">
         <v>15</v>
       </c>
-      <c r="E59" s="1"/>
+      <c r="E59" s="1">
+        <v>36.9</v>
+      </c>
       <c r="F59" s="1">
         <v>10</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1">
+        <v>11.9</v>
+      </c>
       <c r="H59" s="1">
         <v>7.4</v>
       </c>
-      <c r="I59" s="1"/>
+      <c r="I59" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="J59" s="1">
         <v>5</v>
       </c>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="L59" s="1">
         <v>2.8</v>
       </c>
-      <c r="M59" s="1"/>
+      <c r="M59" s="1">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
@@ -2694,23 +2734,33 @@
       <c r="D60" s="1">
         <v>15</v>
       </c>
-      <c r="E60" s="1"/>
+      <c r="E60" s="1">
+        <v>36.9</v>
+      </c>
       <c r="F60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1">
+        <v>12.8</v>
+      </c>
       <c r="H60" s="1">
         <v>7.4</v>
       </c>
-      <c r="I60" s="1"/>
+      <c r="I60" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="J60" s="1">
         <v>5</v>
       </c>
-      <c r="K60" s="1"/>
+      <c r="K60" s="1">
+        <v>1.2</v>
+      </c>
       <c r="L60" s="1">
         <v>2.8</v>
       </c>
-      <c r="M60" s="1"/>
+      <c r="M60" s="1">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
@@ -2726,23 +2776,34 @@
       <c r="D61" s="1">
         <v>15</v>
       </c>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1">
+        <f>37.2</f>
+        <v>37.200000000000003</v>
+      </c>
       <c r="F61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1">
+        <v>12.9</v>
+      </c>
       <c r="H61" s="1">
         <v>7.4</v>
       </c>
-      <c r="I61" s="1"/>
+      <c r="I61" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="J61" s="1">
         <v>5</v>
       </c>
-      <c r="K61" s="1"/>
+      <c r="K61" s="1">
+        <v>1.2</v>
+      </c>
       <c r="L61" s="1">
         <v>2.8</v>
       </c>
-      <c r="M61" s="1"/>
+      <c r="M61" s="1">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
@@ -3940,23 +4001,33 @@
       <c r="D94" s="1">
         <v>22</v>
       </c>
-      <c r="E94" s="1"/>
+      <c r="E94" s="1">
+        <v>25.7</v>
+      </c>
       <c r="F94" s="1">
         <v>6</v>
       </c>
-      <c r="G94" s="1"/>
+      <c r="G94" s="1">
+        <v>11.7</v>
+      </c>
       <c r="H94" s="1">
         <v>4.5</v>
       </c>
-      <c r="I94" s="1"/>
+      <c r="I94" s="1">
+        <v>9.1</v>
+      </c>
       <c r="J94" s="1">
         <v>5</v>
       </c>
-      <c r="K94" s="1"/>
+      <c r="K94" s="1">
+        <v>3.6</v>
+      </c>
       <c r="L94" s="1">
         <v>2.7</v>
       </c>
-      <c r="M94" s="1"/>
+      <c r="M94" s="1">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -3972,23 +4043,33 @@
       <c r="D95" s="1">
         <v>22</v>
       </c>
-      <c r="E95" s="1"/>
+      <c r="E95" s="1">
+        <v>25.7</v>
+      </c>
       <c r="F95" s="1">
         <v>6</v>
       </c>
-      <c r="G95" s="1"/>
+      <c r="G95" s="1">
+        <v>12.2</v>
+      </c>
       <c r="H95" s="1">
         <v>4.5</v>
       </c>
-      <c r="I95" s="1"/>
+      <c r="I95" s="1">
+        <v>9.1</v>
+      </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
-      <c r="K95" s="1"/>
+      <c r="K95" s="1">
+        <v>3.6</v>
+      </c>
       <c r="L95" s="1">
         <v>2.7</v>
       </c>
-      <c r="M95" s="1"/>
+      <c r="M95" s="1">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -4004,23 +4085,33 @@
       <c r="D96" s="1">
         <v>22</v>
       </c>
-      <c r="E96" s="1"/>
+      <c r="E96" s="1">
+        <v>41.3</v>
+      </c>
       <c r="F96" s="1">
         <v>6</v>
       </c>
-      <c r="G96" s="1"/>
+      <c r="G96" s="1">
+        <v>12.2</v>
+      </c>
       <c r="H96" s="1">
         <v>4.5</v>
       </c>
-      <c r="I96" s="1"/>
+      <c r="I96" s="1">
+        <v>9.1</v>
+      </c>
       <c r="J96" s="1">
         <v>5</v>
       </c>
-      <c r="K96" s="1"/>
+      <c r="K96" s="1">
+        <v>3.6</v>
+      </c>
       <c r="L96" s="1">
         <v>2.7</v>
       </c>
-      <c r="M96" s="1"/>
+      <c r="M96" s="1">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E3FCE5-B99F-4572-B2DA-279AF09BB54C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C569C81B-8781-4036-BC55-835BF6F4D1EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1510,23 +1510,33 @@
       <c r="D26" s="1">
         <v>45</v>
       </c>
-      <c r="E26" s="1"/>
+      <c r="E26" s="1">
+        <v>79.400000000000006</v>
+      </c>
       <c r="F26" s="1">
         <v>35.1</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1">
+        <v>44.4</v>
+      </c>
       <c r="H26" s="1">
         <v>30</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1">
+        <v>44.6</v>
+      </c>
       <c r="J26" s="1">
         <v>12</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1">
+        <v>7.6</v>
+      </c>
       <c r="L26" s="1">
         <v>13.5</v>
       </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1785,21 +1795,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1843,13 +1853,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1874,9 +1884,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2819,23 +2829,33 @@
       <c r="D62" s="1">
         <v>15</v>
       </c>
-      <c r="E62" s="1"/>
+      <c r="E62" s="1">
+        <v>45.2</v>
+      </c>
       <c r="F62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1">
+        <v>10.7</v>
+      </c>
       <c r="H62" s="1">
         <v>7.4</v>
       </c>
-      <c r="I62" s="1"/>
+      <c r="I62" s="1">
+        <v>13.5</v>
+      </c>
       <c r="J62" s="1">
         <v>5</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="1">
+        <v>11.1</v>
+      </c>
       <c r="L62" s="1">
         <v>2.8</v>
       </c>
-      <c r="M62" s="1"/>
+      <c r="M62" s="1">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -3094,21 +3114,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3152,13 +3172,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3183,9 +3203,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -4127,23 +4147,34 @@
       <c r="D97" s="1">
         <v>22</v>
       </c>
-      <c r="E97" s="1"/>
+      <c r="E97" s="1">
+        <f>36.9</f>
+        <v>36.9</v>
+      </c>
       <c r="F97" s="1">
         <v>6</v>
       </c>
-      <c r="G97" s="1"/>
+      <c r="G97" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="H97" s="1">
         <v>4.5</v>
       </c>
-      <c r="I97" s="1"/>
+      <c r="I97" s="1">
+        <v>6.9</v>
+      </c>
       <c r="J97" s="1">
         <v>5</v>
       </c>
-      <c r="K97" s="1"/>
+      <c r="K97" s="1">
+        <v>10.7</v>
+      </c>
       <c r="L97" s="1">
         <v>2.7</v>
       </c>
-      <c r="M97" s="1"/>
+      <c r="M97" s="1">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -4403,6 +4434,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4412,24 +4461,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C569C81B-8781-4036-BC55-835BF6F4D1EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5574C646-A60D-41E3-9F05-20F3F0C3C69B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1552,23 +1552,34 @@
       <c r="D27" s="1">
         <v>45</v>
       </c>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1">
+        <f>70.7</f>
+        <v>70.7</v>
+      </c>
       <c r="F27" s="1">
         <v>35.1</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1">
+        <v>36.6</v>
+      </c>
       <c r="H27" s="1">
         <v>30</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1">
+        <v>52.1</v>
+      </c>
       <c r="J27" s="1">
         <v>12</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1">
+        <v>14.4</v>
+      </c>
       <c r="L27" s="1">
         <v>13.5</v>
       </c>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1">
+        <v>19.600000000000001</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1795,21 +1806,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1853,13 +1864,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1884,9 +1895,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2871,23 +2882,34 @@
       <c r="D63" s="1">
         <v>15</v>
       </c>
-      <c r="E63" s="1"/>
+      <c r="E63" s="1">
+        <f>36.4</f>
+        <v>36.4</v>
+      </c>
       <c r="F63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1">
+        <v>14.6</v>
+      </c>
       <c r="H63" s="1">
         <v>7.4</v>
       </c>
-      <c r="I63" s="1"/>
+      <c r="I63" s="1">
+        <v>10.8</v>
+      </c>
       <c r="J63" s="1">
         <v>5</v>
       </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="1">
+        <v>5.8</v>
+      </c>
       <c r="L63" s="1">
         <v>2.8</v>
       </c>
-      <c r="M63" s="1"/>
+      <c r="M63" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
@@ -3114,21 +3136,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3172,13 +3194,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3203,9 +3225,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -4190,23 +4212,34 @@
       <c r="D98" s="1">
         <v>22</v>
       </c>
-      <c r="E98" s="1"/>
+      <c r="E98" s="1">
+        <f>29.6</f>
+        <v>29.6</v>
+      </c>
       <c r="F98" s="1">
         <v>6</v>
       </c>
-      <c r="G98" s="1"/>
+      <c r="G98" s="1">
+        <v>14.2</v>
+      </c>
       <c r="H98" s="1">
         <v>4.5</v>
       </c>
-      <c r="I98" s="1"/>
+      <c r="I98" s="1">
+        <v>20</v>
+      </c>
       <c r="J98" s="1">
         <v>5</v>
       </c>
-      <c r="K98" s="1"/>
+      <c r="K98" s="1">
+        <v>6.8</v>
+      </c>
       <c r="L98" s="1">
         <v>2.7</v>
       </c>
-      <c r="M98" s="1"/>
+      <c r="M98" s="1">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -4434,6 +4467,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -4443,24 +4494,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5574C646-A60D-41E3-9F05-20F3F0C3C69B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7063E14-DFA7-4294-A12A-48D594DAC994}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1595,23 +1595,34 @@
       <c r="D28" s="1">
         <v>45</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <f>50.2+33</f>
+        <v>83.2</v>
+      </c>
       <c r="F28" s="1">
         <v>35.1</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1">
+        <v>39.9</v>
+      </c>
       <c r="H28" s="1">
         <v>30</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>56.4</v>
+      </c>
       <c r="J28" s="1">
         <v>12</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="L28" s="1">
         <v>13.5</v>
       </c>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1806,21 +1817,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1864,13 +1875,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1895,9 +1906,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2925,23 +2936,34 @@
       <c r="D64" s="1">
         <v>15</v>
       </c>
-      <c r="E64" s="1"/>
+      <c r="E64" s="1">
+        <f>29.7+15</f>
+        <v>44.7</v>
+      </c>
       <c r="F64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1">
+        <v>13.3</v>
+      </c>
       <c r="H64" s="1">
         <v>7.4</v>
       </c>
-      <c r="I64" s="1"/>
+      <c r="I64" s="1">
+        <v>21.6</v>
+      </c>
       <c r="J64" s="1">
         <v>5</v>
       </c>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="L64" s="1">
         <v>2.8</v>
       </c>
-      <c r="M64" s="1"/>
+      <c r="M64" s="1">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -3136,21 +3158,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3194,13 +3216,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3225,9 +3247,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -4255,23 +4277,34 @@
       <c r="D99" s="1">
         <v>22</v>
       </c>
-      <c r="E99" s="1"/>
+      <c r="E99" s="1">
+        <f>38.4</f>
+        <v>38.4</v>
+      </c>
       <c r="F99" s="1">
         <v>6</v>
       </c>
-      <c r="G99" s="1"/>
+      <c r="G99" s="1">
+        <v>15.3</v>
+      </c>
       <c r="H99" s="1">
         <v>4.5</v>
       </c>
-      <c r="I99" s="1"/>
+      <c r="I99" s="1">
+        <v>19.100000000000001</v>
+      </c>
       <c r="J99" s="1">
         <v>5</v>
       </c>
-      <c r="K99" s="1"/>
+      <c r="K99" s="1">
+        <v>6.1</v>
+      </c>
       <c r="L99" s="1">
         <v>2.7</v>
       </c>
-      <c r="M99" s="1"/>
+      <c r="M99" s="1">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -4467,6 +4500,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4476,24 +4527,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7063E14-DFA7-4294-A12A-48D594DAC994}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF3C5C7-0219-4CBD-854A-FE82B60F2684}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1638,23 +1638,34 @@
       <c r="D29" s="1">
         <v>45</v>
       </c>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1">
+        <f>60.1+17.5</f>
+        <v>77.599999999999994</v>
+      </c>
       <c r="F29" s="1">
         <v>35.1</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <v>47.5</v>
+      </c>
       <c r="H29" s="1">
         <v>30</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1">
+        <v>48.3</v>
+      </c>
       <c r="J29" s="1">
         <v>12</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1">
+        <v>8</v>
+      </c>
       <c r="L29" s="1">
         <v>13.5</v>
       </c>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2979,23 +2990,34 @@
       <c r="D65" s="1">
         <v>15</v>
       </c>
-      <c r="E65" s="1"/>
+      <c r="E65" s="1">
+        <f>38</f>
+        <v>38</v>
+      </c>
       <c r="F65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1">
+        <v>17.2</v>
+      </c>
       <c r="H65" s="1">
         <v>7.4</v>
       </c>
-      <c r="I65" s="1"/>
+      <c r="I65" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="J65" s="1">
         <v>5</v>
       </c>
-      <c r="K65" s="1"/>
+      <c r="K65" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L65" s="1">
         <v>2.8</v>
       </c>
-      <c r="M65" s="1"/>
+      <c r="M65" s="1">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
@@ -4320,23 +4342,34 @@
       <c r="D100" s="1">
         <v>22</v>
       </c>
-      <c r="E100" s="1"/>
+      <c r="E100" s="1">
+        <f>30.7+6</f>
+        <v>36.700000000000003</v>
+      </c>
       <c r="F100" s="1">
         <v>6</v>
       </c>
-      <c r="G100" s="1"/>
+      <c r="G100" s="1">
+        <v>13.2</v>
+      </c>
       <c r="H100" s="1">
         <v>4.5</v>
       </c>
-      <c r="I100" s="1"/>
+      <c r="I100" s="1">
+        <v>17.7</v>
+      </c>
       <c r="J100" s="1">
         <v>5</v>
       </c>
-      <c r="K100" s="1"/>
+      <c r="K100" s="1">
+        <v>5.7</v>
+      </c>
       <c r="L100" s="1">
         <v>2.7</v>
       </c>
-      <c r="M100" s="1"/>
+      <c r="M100" s="1">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF3C5C7-0219-4CBD-854A-FE82B60F2684}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBA00D5-38F9-4369-940F-0D64A8144DFD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1681,23 +1681,33 @@
       <c r="D30" s="1">
         <v>45</v>
       </c>
-      <c r="E30" s="1"/>
+      <c r="E30" s="1">
+        <v>39.5</v>
+      </c>
       <c r="F30" s="1">
         <v>35.1</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1">
+        <v>55.6</v>
+      </c>
       <c r="H30" s="1">
         <v>30</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1">
+        <v>41.7</v>
+      </c>
       <c r="J30" s="1">
         <v>12</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1">
+        <v>6.8</v>
+      </c>
       <c r="L30" s="1">
         <v>13.5</v>
       </c>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -1713,23 +1723,33 @@
       <c r="D31" s="1">
         <v>45</v>
       </c>
-      <c r="E31" s="1"/>
+      <c r="E31" s="1">
+        <v>39.5</v>
+      </c>
       <c r="F31" s="1">
         <v>35.1</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1">
+        <v>55.7</v>
+      </c>
       <c r="H31" s="1">
         <v>30</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>41.4</v>
+      </c>
       <c r="J31" s="1">
         <v>12</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="1">
+        <v>6.8</v>
+      </c>
       <c r="L31" s="1">
         <v>13.5</v>
       </c>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -1745,23 +1765,33 @@
       <c r="D32" s="1">
         <v>45</v>
       </c>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <v>57.4</v>
+      </c>
       <c r="F32" s="1">
         <v>35.1</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1">
+        <v>55.8</v>
+      </c>
       <c r="H32" s="1">
         <v>30</v>
       </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1">
+        <v>41.4</v>
+      </c>
       <c r="J32" s="1">
         <v>12</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1">
+        <v>6.8</v>
+      </c>
       <c r="L32" s="1">
         <v>13.5</v>
       </c>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -1828,21 +1858,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1886,13 +1916,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1917,9 +1947,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -3033,23 +3063,33 @@
       <c r="D66" s="1">
         <v>15</v>
       </c>
-      <c r="E66" s="1"/>
+      <c r="E66" s="1">
+        <v>33.4</v>
+      </c>
       <c r="F66" s="1">
         <v>10</v>
       </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1">
+        <v>13.8</v>
+      </c>
       <c r="H66" s="1">
         <v>7.4</v>
       </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="1">
+        <v>17.8</v>
+      </c>
       <c r="J66" s="1">
         <v>5</v>
       </c>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="L66" s="1">
         <v>2.8</v>
       </c>
-      <c r="M66" s="1"/>
+      <c r="M66" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
@@ -3065,23 +3105,33 @@
       <c r="D67" s="1">
         <v>15</v>
       </c>
-      <c r="E67" s="1"/>
+      <c r="E67" s="1">
+        <v>33.4</v>
+      </c>
       <c r="F67" s="1">
         <v>10</v>
       </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1">
+        <v>13.8</v>
+      </c>
       <c r="H67" s="1">
         <v>7.4</v>
       </c>
-      <c r="I67" s="1"/>
+      <c r="I67" s="1">
+        <v>18</v>
+      </c>
       <c r="J67" s="1">
         <v>5</v>
       </c>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="L67" s="1">
         <v>2.8</v>
       </c>
-      <c r="M67" s="1"/>
+      <c r="M67" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
@@ -3097,23 +3147,34 @@
       <c r="D68" s="1">
         <v>15</v>
       </c>
-      <c r="E68" s="1"/>
+      <c r="E68" s="1">
+        <f>33.4</f>
+        <v>33.4</v>
+      </c>
       <c r="F68" s="1">
         <v>10</v>
       </c>
-      <c r="G68" s="1"/>
+      <c r="G68" s="1">
+        <v>14</v>
+      </c>
       <c r="H68" s="1">
         <v>7.4</v>
       </c>
-      <c r="I68" s="1"/>
+      <c r="I68" s="1">
+        <v>18</v>
+      </c>
       <c r="J68" s="1">
         <v>5</v>
       </c>
-      <c r="K68" s="1"/>
+      <c r="K68" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="L68" s="1">
         <v>2.8</v>
       </c>
-      <c r="M68" s="1"/>
+      <c r="M68" s="1">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
@@ -3180,21 +3241,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -3238,13 +3299,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -3269,9 +3330,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -4385,23 +4446,33 @@
       <c r="D101" s="1">
         <v>22</v>
       </c>
-      <c r="E101" s="1"/>
+      <c r="E101" s="1">
+        <v>31.4</v>
+      </c>
       <c r="F101" s="1">
         <v>6</v>
       </c>
-      <c r="G101" s="1"/>
+      <c r="G101" s="1">
+        <v>13</v>
+      </c>
       <c r="H101" s="1">
         <v>4.5</v>
       </c>
-      <c r="I101" s="1"/>
+      <c r="I101" s="1">
+        <v>16.3</v>
+      </c>
       <c r="J101" s="1">
         <v>5</v>
       </c>
-      <c r="K101" s="1"/>
+      <c r="K101" s="1">
+        <v>8.4</v>
+      </c>
       <c r="L101" s="1">
         <v>2.7</v>
       </c>
-      <c r="M101" s="1"/>
+      <c r="M101" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -4417,23 +4488,33 @@
       <c r="D102" s="1">
         <v>22</v>
       </c>
-      <c r="E102" s="1"/>
+      <c r="E102" s="1">
+        <v>31.4</v>
+      </c>
       <c r="F102" s="1">
         <v>6</v>
       </c>
-      <c r="G102" s="1"/>
+      <c r="G102" s="1">
+        <v>13</v>
+      </c>
       <c r="H102" s="1">
         <v>4.5</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="J102" s="1">
         <v>5</v>
       </c>
-      <c r="K102" s="1"/>
+      <c r="K102" s="1">
+        <v>8.4</v>
+      </c>
       <c r="L102" s="1">
         <v>2.7</v>
       </c>
-      <c r="M102" s="1"/>
+      <c r="M102" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -4449,23 +4530,33 @@
       <c r="D103" s="1">
         <v>22</v>
       </c>
-      <c r="E103" s="1"/>
+      <c r="E103" s="1">
+        <v>35.299999999999997</v>
+      </c>
       <c r="F103" s="1">
         <v>6</v>
       </c>
-      <c r="G103" s="1"/>
+      <c r="G103" s="1">
+        <v>13</v>
+      </c>
       <c r="H103" s="1">
         <v>4.5</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="J103" s="1">
         <v>5</v>
       </c>
-      <c r="K103" s="1"/>
+      <c r="K103" s="1">
+        <v>8.4</v>
+      </c>
       <c r="L103" s="1">
         <v>2.7</v>
       </c>
-      <c r="M103" s="1"/>
+      <c r="M103" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -4533,6 +4624,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -4542,24 +4651,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBA00D5-38F9-4369-940F-0D64A8144DFD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9033E87F-083B-4E4F-8604-B834DA8630DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1807,23 +1807,34 @@
       <c r="D33" s="1">
         <v>45</v>
       </c>
-      <c r="E33" s="1"/>
+      <c r="E33" s="1">
+        <f>66.5+17.5</f>
+        <v>84</v>
+      </c>
       <c r="F33" s="1">
         <v>35.1</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1">
+        <v>55.4</v>
+      </c>
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>48.6</v>
+      </c>
       <c r="J33" s="1">
         <v>12</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1">
+        <v>22.6</v>
+      </c>
       <c r="L33" s="1">
         <v>13.5</v>
       </c>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
@@ -3190,23 +3201,33 @@
       <c r="D69" s="1">
         <v>15</v>
       </c>
-      <c r="E69" s="1"/>
+      <c r="E69" s="1">
+        <v>26.8</v>
+      </c>
       <c r="F69" s="1">
         <v>10</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1">
+        <v>11.5</v>
+      </c>
       <c r="H69" s="1">
         <v>7.4</v>
       </c>
-      <c r="I69" s="1"/>
+      <c r="I69" s="1">
+        <v>15.4</v>
+      </c>
       <c r="J69" s="1">
         <v>5</v>
       </c>
-      <c r="K69" s="1"/>
+      <c r="K69" s="1">
+        <v>7.5</v>
+      </c>
       <c r="L69" s="1">
         <v>2.8</v>
       </c>
-      <c r="M69" s="1"/>
+      <c r="M69" s="1">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
@@ -4572,23 +4593,34 @@
       <c r="D104" s="1">
         <v>22</v>
       </c>
-      <c r="E104" s="1"/>
+      <c r="E104" s="1">
+        <f>33.1</f>
+        <v>33.1</v>
+      </c>
       <c r="F104" s="1">
         <v>6</v>
       </c>
-      <c r="G104" s="1"/>
+      <c r="G104" s="1">
+        <v>15.3</v>
+      </c>
       <c r="H104" s="1">
         <v>4.5</v>
       </c>
-      <c r="I104" s="1"/>
+      <c r="I104" s="1">
+        <v>13.8</v>
+      </c>
       <c r="J104" s="1">
         <v>5</v>
       </c>
-      <c r="K104" s="1"/>
+      <c r="K104" s="1">
+        <v>7.9</v>
+      </c>
       <c r="L104" s="1">
         <v>2.7</v>
       </c>
-      <c r="M104" s="1"/>
+      <c r="M104" s="1">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9033E87F-083B-4E4F-8604-B834DA8630DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B17BF4-7A5E-4951-85D4-D8F941A3DEB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1850,23 +1850,34 @@
       <c r="D34" s="1">
         <v>45</v>
       </c>
-      <c r="E34" s="1"/>
+      <c r="E34" s="1">
+        <f>39.5+33</f>
+        <v>72.5</v>
+      </c>
       <c r="F34" s="1">
         <v>35.1</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1">
+        <v>39.5</v>
+      </c>
       <c r="H34" s="1">
         <v>30</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1">
+        <v>39.700000000000003</v>
+      </c>
       <c r="J34" s="1">
         <v>12</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1">
+        <v>12.9</v>
+      </c>
       <c r="L34" s="1">
         <v>13.5</v>
       </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
@@ -3243,23 +3254,34 @@
       <c r="D70" s="1">
         <v>15</v>
       </c>
-      <c r="E70" s="1"/>
+      <c r="E70" s="1">
+        <f>31.7</f>
+        <v>31.7</v>
+      </c>
       <c r="F70" s="1">
         <v>10</v>
       </c>
-      <c r="G70" s="1"/>
+      <c r="G70" s="1">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="H70" s="1">
         <v>7.4</v>
       </c>
-      <c r="I70" s="1"/>
+      <c r="I70" s="1">
+        <v>13.1</v>
+      </c>
       <c r="J70" s="1">
         <v>5</v>
       </c>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1">
+        <v>6.9</v>
+      </c>
       <c r="L70" s="1">
         <v>2.8</v>
       </c>
-      <c r="M70" s="1"/>
+      <c r="M70" s="1">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
@@ -4636,23 +4658,34 @@
       <c r="D105" s="1">
         <v>22</v>
       </c>
-      <c r="E105" s="1"/>
+      <c r="E105" s="1">
+        <f>25.8+10</f>
+        <v>35.799999999999997</v>
+      </c>
       <c r="F105" s="1">
         <v>6</v>
       </c>
-      <c r="G105" s="1"/>
+      <c r="G105" s="1">
+        <v>17.2</v>
+      </c>
       <c r="H105" s="1">
         <v>4.5</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <v>13</v>
+      </c>
       <c r="J105" s="1">
         <v>5</v>
       </c>
-      <c r="K105" s="1"/>
+      <c r="K105" s="1">
+        <v>7.2</v>
+      </c>
       <c r="L105" s="1">
         <v>2.7</v>
       </c>
-      <c r="M105" s="1"/>
+      <c r="M105" s="1">
+        <v>7.2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="27">
